--- a/Tabela_investimento.xlsx
+++ b/Tabela_investimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaior\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FC1522-573A-42DF-AA69-C5C48D5E31F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D499D44-5570-41F3-98FF-8F9DC32F982E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{949F1AF8-4AD5-4D6D-9F04-B593816308E6}"/>
   </bookViews>
@@ -758,7 +758,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -803,89 +803,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -896,6 +816,84 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1293,78 +1291,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20670155-0CB8-4923-8BC2-64C0BDA73669}">
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.21875" customWidth="1"/>
     <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="3.5546875" customWidth="1"/>
-    <col min="6" max="6" width="3.44140625" customWidth="1"/>
-    <col min="7" max="7" width="2.77734375" customWidth="1"/>
-    <col min="8" max="8" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="1" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="2" customWidth="1"/>
+    <col min="8" max="16384" width="2.5546875" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
     </row>
     <row r="9" spans="2:4" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="38">
         <v>2500</v>
       </c>
-      <c r="D9" s="45"/>
+      <c r="D9" s="39"/>
     </row>
     <row r="10" spans="2:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="40">
         <v>0.01</v>
       </c>
-      <c r="D10" s="47"/>
+      <c r="D10" s="41"/>
     </row>
     <row r="11" spans="2:4" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="53">
         <f>Salario*30%</f>
         <v>750</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="54"/>
     </row>
     <row r="12" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:4" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="56"/>
     </row>
     <row r="14" spans="2:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="57">
         <f>C11</f>
         <v>750</v>
       </c>
-      <c r="D14" s="38"/>
+      <c r="D14" s="58"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
@@ -1563,66 +1558,66 @@
       </c>
     </row>
     <row r="33" spans="2:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="51"/>
-      <c r="D33" s="52"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="46"/>
     </row>
     <row r="34" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="59">
         <f>C11</f>
         <v>750</v>
       </c>
-      <c r="D34" s="40"/>
+      <c r="D34" s="60"/>
     </row>
     <row r="35" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="61">
         <v>5</v>
       </c>
-      <c r="D35" s="42"/>
+      <c r="D35" s="62"/>
     </row>
     <row r="36" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="47">
         <f>Rendimento_Carteira</f>
         <v>0.01</v>
       </c>
-      <c r="D36" s="29"/>
+      <c r="D36" s="48"/>
     </row>
     <row r="37" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="49">
         <f>FV(Taxa_mensal,Anos*12,Investimento_mensal)*-1</f>
         <v>61252.252392306844</v>
       </c>
-      <c r="D37" s="31"/>
+      <c r="D37" s="50"/>
     </row>
     <row r="38" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="42">
         <f>Patrimonio_acumulado*Rendimento_Carteira</f>
         <v>612.52252392306843</v>
       </c>
-      <c r="D38" s="49"/>
+      <c r="D38" s="43"/>
     </row>
     <row r="40" spans="2:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="53"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="3" t="s">
         <v>10</v>
       </c>
@@ -1697,6 +1692,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
@@ -1704,12 +1705,6 @@
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13" xr:uid="{5518B0CD-D26B-44CD-9DAA-11261F6C7397}">
@@ -1738,16 +1733,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="61" t="s">
+      <c r="E3" s="33" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1762,7 +1757,7 @@
       <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="28">
         <v>0.3</v>
       </c>
     </row>
@@ -1777,21 +1772,21 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="28">
         <v>0.5</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="55" t="s">
+      <c r="I5" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="63" t="str">
+      <c r="B6" s="35" t="str">
         <f>C6&amp;"-"&amp;D6</f>
         <v>Conservador-HÍBRIDO</v>
       </c>
@@ -1801,16 +1796,16 @@
       <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="36">
         <v>0.1</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="58">
+      <c r="H6" s="28">
         <v>0.2</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="28">
         <v>0.8</v>
       </c>
     </row>
@@ -1825,16 +1820,16 @@
       <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="28">
         <v>0.1</v>
       </c>
-      <c r="G7" s="57" t="s">
+      <c r="G7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="28">
         <v>0.35</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7" s="28">
         <v>0.65</v>
       </c>
     </row>
@@ -1849,16 +1844,16 @@
       <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="28">
         <v>0</v>
       </c>
-      <c r="G8" s="59" t="s">
+      <c r="G8" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="32">
         <v>0.5</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="32">
         <v>0.5</v>
       </c>
     </row>
@@ -1873,97 +1868,97 @@
       <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="55" t="str">
+      <c r="B10" s="29" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-PAPEL</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="30">
         <v>0.32</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="57" t="str">
+      <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-TIJOLO</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="57" t="s">
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="28">
         <v>0.35</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="57" t="str">
+      <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-HÍBRIDO</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="28">
         <v>0.08</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="57" t="str">
+      <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-FOFs</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E13" s="28">
         <v>0.05</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="57" t="str">
+      <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-DESENVOLVIMENTO</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="28">
         <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="59" t="str">
+      <c r="B15" s="31" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-HOTELARIAS</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="32">
         <v>0.1</v>
       </c>
     </row>
@@ -1978,7 +1973,7 @@
       <c r="D16" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="28">
         <v>0.5</v>
       </c>
     </row>
@@ -1993,7 +1988,7 @@
       <c r="D17" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="28">
         <v>0.1</v>
       </c>
     </row>
@@ -2008,7 +2003,7 @@
       <c r="D18" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="28">
         <v>0.05</v>
       </c>
     </row>
@@ -2023,7 +2018,7 @@
       <c r="D19" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="28">
         <v>0.05</v>
       </c>
     </row>
@@ -2038,7 +2033,7 @@
       <c r="D20" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="28">
         <v>0.2</v>
       </c>
     </row>
@@ -2053,29 +2048,29 @@
       <c r="D21" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="28">
         <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="62"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D23" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="61" t="s">
+      <c r="E23" s="33" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2090,7 +2085,7 @@
       <c r="D24" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="28">
         <v>0.35</v>
       </c>
     </row>
@@ -2105,7 +2100,7 @@
       <c r="D25" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="28">
         <v>0.3</v>
       </c>
     </row>
@@ -2120,7 +2115,7 @@
       <c r="D26" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="28">
         <v>0.25</v>
       </c>
     </row>
@@ -2135,7 +2130,7 @@
       <c r="D27" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="54">
+      <c r="E27" s="28">
         <v>0.05</v>
       </c>
     </row>
@@ -2150,82 +2145,82 @@
       <c r="D28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="28">
         <v>0.05</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="55" t="str">
+      <c r="B29" s="29" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-Tesouro Direto</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="56">
+      <c r="E29" s="30">
         <v>0.25</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="57" t="str">
+      <c r="B30" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-CDB</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="58">
+      <c r="E30" s="28">
         <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="57" t="str">
+      <c r="B31" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-LCI e LCA</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="58">
+      <c r="E31" s="28">
         <v>0.2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="57" t="str">
+      <c r="B32" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-CRI e CRA</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="58">
+      <c r="E32" s="28">
         <v>0.15</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="59" t="str">
+      <c r="B33" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-Dedêntures</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="60">
+      <c r="E33" s="32">
         <v>0.15</v>
       </c>
     </row>
@@ -2240,7 +2235,7 @@
       <c r="D34" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="54">
+      <c r="E34" s="28">
         <v>0.15</v>
       </c>
     </row>
@@ -2255,7 +2250,7 @@
       <c r="D35" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="54">
+      <c r="E35" s="28">
         <v>0.2</v>
       </c>
     </row>
@@ -2270,7 +2265,7 @@
       <c r="D36" t="s">
         <v>30</v>
       </c>
-      <c r="E36" s="54">
+      <c r="E36" s="28">
         <v>0.15</v>
       </c>
     </row>
@@ -2285,7 +2280,7 @@
       <c r="D37" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="54">
+      <c r="E37" s="28">
         <v>0.25</v>
       </c>
     </row>
@@ -2300,7 +2295,7 @@
       <c r="D38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="28">
         <v>0.25</v>
       </c>
     </row>
